--- a/data_indexpoints_tidy/tallmateriale_20952.xlsx
+++ b/data_indexpoints_tidy/tallmateriale_20952.xlsx
@@ -2554,6 +2554,9 @@
       <c r="F3">
         <v>0.95</v>
       </c>
+      <c r="G3">
+        <v>3.71</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2636,6 +2639,9 @@
       <c r="F5">
         <v>-1.41</v>
       </c>
+      <c r="G5">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2718,6 +2724,9 @@
       <c r="F7">
         <v>-0.14</v>
       </c>
+      <c r="G7">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2800,6 +2809,9 @@
       <c r="F9">
         <v>-0.84</v>
       </c>
+      <c r="G9">
+        <v>1.21</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2882,6 +2894,9 @@
       <c r="F11">
         <v>11.73</v>
       </c>
+      <c r="G11">
+        <v>15.11</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2946,6 +2961,9 @@
       <c r="F13">
         <v>-5.24</v>
       </c>
+      <c r="G13">
+        <v>-1.39</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3025,6 +3043,9 @@
       <c r="F15">
         <v>-0.52</v>
       </c>
+      <c r="G15">
+        <v>2.14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3168,6 +3189,9 @@
       <c r="F19">
         <v>0.71</v>
       </c>
+      <c r="G19">
+        <v>4.52</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3232,6 +3256,9 @@
       <c r="F21">
         <v>6.61</v>
       </c>
+      <c r="G21">
+        <v>6.07</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3314,6 +3341,9 @@
       <c r="F23">
         <v>-6.9</v>
       </c>
+      <c r="G23">
+        <v>-3.52</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3378,6 +3408,9 @@
       <c r="F25">
         <v>7.86</v>
       </c>
+      <c r="G25">
+        <v>11.25</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3518,6 +3551,9 @@
       <c r="F29">
         <v>6.52</v>
       </c>
+      <c r="G29">
+        <v>8.390000000000001</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3600,6 +3636,9 @@
       <c r="F31">
         <v>-8.42</v>
       </c>
+      <c r="G31">
+        <v>-9.039999999999999</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3682,6 +3721,9 @@
       <c r="F33">
         <v>7.24</v>
       </c>
+      <c r="G33">
+        <v>9.1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3761,6 +3803,9 @@
       <c r="F35">
         <v>15.91</v>
       </c>
+      <c r="G35">
+        <v>17.19</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3840,6 +3885,9 @@
       <c r="F37">
         <v>-13</v>
       </c>
+      <c r="G37">
+        <v>-13.35</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3919,6 +3967,9 @@
       <c r="F39">
         <v>-6.71</v>
       </c>
+      <c r="G39">
+        <v>-4.84</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4001,6 +4052,9 @@
       <c r="F41">
         <v>-0.28</v>
       </c>
+      <c r="G41">
+        <v>3.76</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4071,6 +4125,9 @@
       <c r="F43">
         <v>1.76</v>
       </c>
+      <c r="G43">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4153,6 +4210,9 @@
       <c r="F45">
         <v>-0.86</v>
       </c>
+      <c r="G45">
+        <v>0.92</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4235,6 +4295,9 @@
       <c r="F47">
         <v>-5.42</v>
       </c>
+      <c r="G47">
+        <v>-3.23</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4317,6 +4380,9 @@
       <c r="F49">
         <v>2.7</v>
       </c>
+      <c r="G49">
+        <v>2.13</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4399,6 +4465,9 @@
       <c r="F51">
         <v>-2.08</v>
       </c>
+      <c r="G51">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4463,6 +4532,9 @@
       <c r="F53">
         <v>3.86</v>
       </c>
+      <c r="G53">
+        <v>5.53</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4544,6 +4616,9 @@
       </c>
       <c r="F55">
         <v>2.36</v>
+      </c>
+      <c r="G55">
+        <v>0.98</v>
       </c>
     </row>
   </sheetData>
@@ -4690,19 +4765,19 @@
         <v>2026</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E3">
-        <v>1.0138</v>
+        <v>1.0165</v>
       </c>
       <c r="F3">
         <v>25</v>
       </c>
       <c r="G3">
-        <v>1.432537220861701</v>
+        <v>1.408487961412497</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4721,19 +4796,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>feb</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>jan-feb</t>
+          <t>jan-mar</t>
         </is>
       </c>
       <c r="M3">
-        <v>-1.4</v>
+        <v>-1.2</v>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
     </row>
   </sheetData>
@@ -4826,19 +4901,19 @@
         <v>2025</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="E2">
-        <v>1.0124</v>
+        <v>1.0257</v>
       </c>
       <c r="F2">
         <v>27</v>
       </c>
       <c r="G2">
-        <v>0.5360458535073775</v>
+        <v>0.5565788764740937</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -4857,19 +4932,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>feb</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>jan-feb</t>
+          <t>jan-mar</t>
         </is>
       </c>
       <c r="M2">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="N2">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
@@ -4880,19 +4955,19 @@
         <v>2026</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E3">
-        <v>1.0138</v>
+        <v>1.0165</v>
       </c>
       <c r="F3">
         <v>25</v>
       </c>
       <c r="G3">
-        <v>1.432537220861701</v>
+        <v>1.408487961412497</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4911,19 +4986,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>feb</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>jan-feb</t>
+          <t>jan-mar</t>
         </is>
       </c>
       <c r="M3">
-        <v>-1.4</v>
+        <v>-1.2</v>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="4">
@@ -4934,19 +5009,19 @@
         <v>2026</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="E4">
-        <v>1.02637112</v>
+        <v>1.04262405</v>
       </c>
       <c r="F4">
         <v>27</v>
       </c>
       <c r="G4">
-        <v>1.548793608808766</v>
+        <v>1.551536823149577</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -4965,19 +5040,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>feb</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>jan-feb</t>
+          <t>jan-mar</t>
         </is>
       </c>
       <c r="M4">
-        <v>-0.4</v>
+        <v>1.3</v>
       </c>
       <c r="N4">
-        <v>5.6</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -4987,7 +5062,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
@@ -5195,6 +5270,51 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5">
+        <v>1.011926834967251</v>
+      </c>
+      <c r="B5">
+        <v>1.192683496725144</v>
+      </c>
+      <c r="C5">
+        <v>18</v>
+      </c>
+      <c r="D5">
+        <v>9.947184730050116</v>
+      </c>
+      <c r="E5">
+        <v>2.666287333997263</v>
+      </c>
+      <c r="F5">
+        <v>0.8453895164929085</v>
+      </c>
+      <c r="G5">
+        <v>-0.6</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2024 - (apr 2025 - mar 2026)</t>
+        </is>
+      </c>
+      <c r="J5" s="2">
+        <v>46082</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2026</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>12_months</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_indexpoints_tidy/tallmateriale_20952.xlsx
+++ b/data_indexpoints_tidy/tallmateriale_20952.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Programmering\R\byindeks\data_indexpoints_tidy\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0963C8B1-773F-429D-A683-1FEA0B1C99B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="punkt_adt" sheetId="1" r:id="rId1"/>
@@ -19,12 +13,12 @@
     <sheet name="byindeks_hittil" sheetId="4" r:id="rId4"/>
     <sheet name="by_glid_indeks" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="186">
   <si>
     <t>trp_id</t>
   </si>
@@ -476,64 +470,76 @@
     <t>des</t>
   </si>
   <si>
+    <t>area_name</t>
+  </si>
+  <si>
     <t>year_base</t>
   </si>
   <si>
+    <t>year_from_to</t>
+  </si>
+  <si>
     <t>month</t>
   </si>
   <si>
+    <t>month_name_short</t>
+  </si>
+  <si>
+    <t>period</t>
+  </si>
+  <si>
+    <t>index_type</t>
+  </si>
+  <si>
+    <t>n_trp</t>
+  </si>
+  <si>
+    <t>index_i</t>
+  </si>
+  <si>
     <t>index_p</t>
   </si>
   <si>
-    <t>index_i</t>
-  </si>
-  <si>
-    <t>n_trp</t>
-  </si>
-  <si>
     <t>standard_error</t>
   </si>
   <si>
-    <t>index_type</t>
-  </si>
-  <si>
-    <t>year_from_to</t>
-  </si>
-  <si>
-    <t>area_name</t>
-  </si>
-  <si>
-    <t>month_name_short</t>
-  </si>
-  <si>
-    <t>period</t>
-  </si>
-  <si>
     <t>ci_lower</t>
   </si>
   <si>
     <t>ci_upper</t>
   </si>
   <si>
+    <t>2024-2025</t>
+  </si>
+  <si>
+    <t>jan-des</t>
+  </si>
+  <si>
     <t>direct</t>
   </si>
   <si>
-    <t>2024-2025</t>
-  </si>
-  <si>
-    <t>jan-des</t>
-  </si>
-  <si>
     <t>2025-2026</t>
   </si>
   <si>
-    <t>jan-apr</t>
+    <t>jan-jul</t>
+  </si>
+  <si>
+    <t>2024-2026</t>
   </si>
   <si>
     <t>chained</t>
   </si>
   <si>
-    <t>2024-2026</t>
+    <t>month_n</t>
+  </si>
+  <si>
+    <t>month_object</t>
+  </si>
+  <si>
+    <t>window</t>
+  </si>
+  <si>
+    <t>index_period</t>
   </si>
   <si>
     <t>n_eff</t>
@@ -545,24 +551,12 @@
     <t>standard_error_p</t>
   </si>
   <si>
-    <t>index_period</t>
-  </si>
-  <si>
-    <t>month_object</t>
-  </si>
-  <si>
-    <t>month_n</t>
-  </si>
-  <si>
-    <t>window</t>
+    <t>12_months</t>
   </si>
   <si>
     <t>2024 - (jan 2025 - des 2025)</t>
   </si>
   <si>
-    <t>12_months</t>
-  </si>
-  <si>
     <t>2024 - (feb 2025 - jan 2026)</t>
   </si>
   <si>
@@ -573,16 +567,25 @@
   </si>
   <si>
     <t>2024 - (mai 2025 - apr 2026)</t>
+  </si>
+  <si>
+    <t>2024 - (jun 2025 - mai 2026)</t>
+  </si>
+  <si>
+    <t>2024 - (jul 2025 - jun 2026)</t>
+  </si>
+  <si>
+    <t>2024 - (aug 2025 - jul 2026)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -631,21 +634,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -683,7 +678,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -717,7 +712,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -752,10 +746,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -928,11 +921,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -982,7 +975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -999,10 +992,10 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>62.470256999999997</v>
+        <v>62.470257</v>
       </c>
       <c r="G2">
-        <v>6.1754800000000003</v>
+        <v>6.17548</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
@@ -1029,7 +1022,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -1046,10 +1039,10 @@
         <v>20</v>
       </c>
       <c r="F3">
-        <v>62.470736000000002</v>
+        <v>62.470736</v>
       </c>
       <c r="G3">
-        <v>6.1819110000000004</v>
+        <v>6.181911</v>
       </c>
       <c r="H3" t="s">
         <v>25</v>
@@ -1076,7 +1069,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1093,10 +1086,10 @@
         <v>20</v>
       </c>
       <c r="F4">
-        <v>62.464714000000001</v>
+        <v>62.464714</v>
       </c>
       <c r="G4">
-        <v>6.3040330000000004</v>
+        <v>6.304033</v>
       </c>
       <c r="H4" t="s">
         <v>29</v>
@@ -1123,7 +1116,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1140,10 +1133,10 @@
         <v>20</v>
       </c>
       <c r="F5">
-        <v>62.470373000000002</v>
+        <v>62.470373</v>
       </c>
       <c r="G5">
-        <v>6.2040959999999998</v>
+        <v>6.204096</v>
       </c>
       <c r="H5" t="s">
         <v>33</v>
@@ -1170,7 +1163,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1187,10 +1180,10 @@
         <v>20</v>
       </c>
       <c r="F6">
-        <v>62.468288000000001</v>
+        <v>62.468288</v>
       </c>
       <c r="G6">
-        <v>6.3523740000000002</v>
+        <v>6.352374</v>
       </c>
       <c r="H6" t="s">
         <v>37</v>
@@ -1217,7 +1210,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -1234,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="F7">
-        <v>62.465254999999999</v>
+        <v>62.465255</v>
       </c>
       <c r="G7">
         <v>6.345561</v>
@@ -1264,7 +1257,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -1281,10 +1274,10 @@
         <v>20</v>
       </c>
       <c r="F8">
-        <v>62.469518000000001</v>
+        <v>62.469518</v>
       </c>
       <c r="G8">
-        <v>6.2424499999999998</v>
+        <v>6.24245</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1311,7 +1304,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>46</v>
       </c>
@@ -1328,10 +1321,10 @@
         <v>20</v>
       </c>
       <c r="F9">
-        <v>62.469534000000003</v>
+        <v>62.469534</v>
       </c>
       <c r="G9">
-        <v>6.2423609999999998</v>
+        <v>6.242361</v>
       </c>
       <c r="H9" t="s">
         <v>49</v>
@@ -1358,7 +1351,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -1375,10 +1368,10 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>62.470855999999998</v>
+        <v>62.470856</v>
       </c>
       <c r="G10">
-        <v>6.2373469999999998</v>
+        <v>6.237347</v>
       </c>
       <c r="H10" t="s">
         <v>53</v>
@@ -1405,7 +1398,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -1425,7 +1418,7 @@
         <v>62.470599</v>
       </c>
       <c r="G11">
-        <v>6.2392149999999997</v>
+        <v>6.239215</v>
       </c>
       <c r="H11" t="s">
         <v>57</v>
@@ -1452,7 +1445,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -1469,10 +1462,10 @@
         <v>20</v>
       </c>
       <c r="F12">
-        <v>62.469661000000002</v>
+        <v>62.469661</v>
       </c>
       <c r="G12">
-        <v>6.2464139999999997</v>
+        <v>6.246414</v>
       </c>
       <c r="H12" t="s">
         <v>61</v>
@@ -1499,7 +1492,7 @@
         <v>2380</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -1516,7 +1509,7 @@
         <v>20</v>
       </c>
       <c r="F13">
-        <v>62.470134999999999</v>
+        <v>62.470135</v>
       </c>
       <c r="G13">
         <v>6.141038</v>
@@ -1546,7 +1539,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -1566,7 +1559,7 @@
         <v>62.470734</v>
       </c>
       <c r="G14">
-        <v>6.1863669999999997</v>
+        <v>6.186367</v>
       </c>
       <c r="H14" t="s">
         <v>69</v>
@@ -1593,7 +1586,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
         <v>70</v>
       </c>
@@ -1610,10 +1603,10 @@
         <v>20</v>
       </c>
       <c r="F15">
-        <v>62.470171000000001</v>
+        <v>62.470171</v>
       </c>
       <c r="G15">
-        <v>6.2033149999999999</v>
+        <v>6.203315</v>
       </c>
       <c r="H15" t="s">
         <v>73</v>
@@ -1640,7 +1633,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>74</v>
       </c>
@@ -1657,10 +1650,10 @@
         <v>20</v>
       </c>
       <c r="F16">
-        <v>62.470351000000001</v>
+        <v>62.470351</v>
       </c>
       <c r="G16">
-        <v>6.1954209999999996</v>
+        <v>6.195421</v>
       </c>
       <c r="H16" t="s">
         <v>77</v>
@@ -1687,7 +1680,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>78</v>
       </c>
@@ -1704,10 +1697,10 @@
         <v>20</v>
       </c>
       <c r="F17">
-        <v>62.470224000000002</v>
+        <v>62.470224</v>
       </c>
       <c r="G17">
-        <v>6.2040990000000003</v>
+        <v>6.204099</v>
       </c>
       <c r="H17" t="s">
         <v>81</v>
@@ -1734,7 +1727,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -1751,10 +1744,10 @@
         <v>20</v>
       </c>
       <c r="F18">
-        <v>62.470180999999997</v>
+        <v>62.470181</v>
       </c>
       <c r="G18">
-        <v>6.1989570000000001</v>
+        <v>6.198957</v>
       </c>
       <c r="H18" t="s">
         <v>85</v>
@@ -1781,7 +1774,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>86</v>
       </c>
@@ -1828,7 +1821,7 @@
         <v>2710</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -1845,7 +1838,7 @@
         <v>20</v>
       </c>
       <c r="F20">
-        <v>62.462347999999999</v>
+        <v>62.462348</v>
       </c>
       <c r="G20">
         <v>6.356992</v>
@@ -1875,7 +1868,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>95</v>
       </c>
@@ -1892,10 +1885,10 @@
         <v>20</v>
       </c>
       <c r="F21">
-        <v>62.470778000000003</v>
+        <v>62.470778</v>
       </c>
       <c r="G21">
-        <v>6.3645259999999997</v>
+        <v>6.364526</v>
       </c>
       <c r="H21" t="s">
         <v>98</v>
@@ -1922,7 +1915,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>99</v>
       </c>
@@ -1939,10 +1932,10 @@
         <v>20</v>
       </c>
       <c r="F22">
-        <v>62.471114999999998</v>
+        <v>62.471115</v>
       </c>
       <c r="G22">
-        <v>6.3548460000000002</v>
+        <v>6.354846</v>
       </c>
       <c r="H22" t="s">
         <v>103</v>
@@ -1969,7 +1962,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>104</v>
       </c>
@@ -1986,10 +1979,10 @@
         <v>20</v>
       </c>
       <c r="F23">
-        <v>62.469059999999999</v>
+        <v>62.46906</v>
       </c>
       <c r="G23">
-        <v>6.2411240000000001</v>
+        <v>6.241124</v>
       </c>
       <c r="H23" t="s">
         <v>108</v>
@@ -2016,7 +2009,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>109</v>
       </c>
@@ -2033,7 +2026,7 @@
         <v>20</v>
       </c>
       <c r="F24">
-        <v>62.471648000000002</v>
+        <v>62.471648</v>
       </c>
       <c r="G24">
         <v>6.214899</v>
@@ -2063,7 +2056,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -2080,10 +2073,10 @@
         <v>20</v>
       </c>
       <c r="F25">
-        <v>62.470838999999998</v>
+        <v>62.470839</v>
       </c>
       <c r="G25">
-        <v>6.3650010000000004</v>
+        <v>6.365001</v>
       </c>
       <c r="H25" t="s">
         <v>117</v>
@@ -2110,7 +2103,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>118</v>
       </c>
@@ -2127,10 +2120,10 @@
         <v>20</v>
       </c>
       <c r="F26">
-        <v>62.438892000000003</v>
+        <v>62.438892</v>
       </c>
       <c r="G26">
-        <v>6.3849980000000004</v>
+        <v>6.384998</v>
       </c>
       <c r="H26" t="s">
         <v>122</v>
@@ -2157,7 +2150,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>123</v>
       </c>
@@ -2174,10 +2167,10 @@
         <v>20</v>
       </c>
       <c r="F27">
-        <v>62.436624999999999</v>
+        <v>62.436625</v>
       </c>
       <c r="G27">
-        <v>6.4426480000000002</v>
+        <v>6.442648</v>
       </c>
       <c r="H27" t="s">
         <v>126</v>
@@ -2204,7 +2197,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>127</v>
       </c>
@@ -2221,10 +2214,10 @@
         <v>20</v>
       </c>
       <c r="F28">
-        <v>62.456921000000001</v>
+        <v>62.456921</v>
       </c>
       <c r="G28">
-        <v>6.3626860000000001</v>
+        <v>6.362686</v>
       </c>
       <c r="H28" t="s">
         <v>131</v>
@@ -2251,7 +2244,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>132</v>
       </c>
@@ -2268,10 +2261,10 @@
         <v>20</v>
       </c>
       <c r="F29">
-        <v>62.471865000000001</v>
+        <v>62.471865</v>
       </c>
       <c r="G29">
-        <v>6.1763669999999999</v>
+        <v>6.176367</v>
       </c>
       <c r="H29" t="s">
         <v>136</v>
@@ -2304,11 +2297,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2358,7 +2351,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2375,7 +2368,7 @@
         <v>3.34</v>
       </c>
       <c r="F2">
-        <v>5.0199999999999996</v>
+        <v>5.02</v>
       </c>
       <c r="G2">
         <v>6.52</v>
@@ -2408,7 +2401,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2422,7 +2415,7 @@
         <v>2026</v>
       </c>
       <c r="E3">
-        <v>5.0599999999999996</v>
+        <v>5.06</v>
       </c>
       <c r="F3">
         <v>0.95</v>
@@ -2433,8 +2426,17 @@
       <c r="H3">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I3">
+        <v>-0.58</v>
+      </c>
+      <c r="J3">
+        <v>5.22</v>
+      </c>
+      <c r="K3">
+        <v>-7.41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -2448,13 +2450,13 @@
         <v>2025</v>
       </c>
       <c r="E4">
-        <v>2.5299999999999998</v>
+        <v>2.53</v>
       </c>
       <c r="F4">
         <v>2.95</v>
       </c>
       <c r="G4">
-        <v>4.8099999999999996</v>
+        <v>4.81</v>
       </c>
       <c r="H4">
         <v>-2.06</v>
@@ -2472,7 +2474,7 @@
         <v>1.03</v>
       </c>
       <c r="M4">
-        <v>2.5299999999999998</v>
+        <v>2.53</v>
       </c>
       <c r="N4">
         <v>0.12</v>
@@ -2484,7 +2486,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -2509,8 +2511,17 @@
       <c r="H5">
         <v>-1.23</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <v>-3.54</v>
+      </c>
+      <c r="J5">
+        <v>2.7</v>
+      </c>
+      <c r="K5">
+        <v>-8.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>118</v>
       </c>
@@ -2527,7 +2538,7 @@
         <v>3.43</v>
       </c>
       <c r="F6">
-        <v>2.5299999999999998</v>
+        <v>2.53</v>
       </c>
       <c r="G6">
         <v>6.26</v>
@@ -2539,10 +2550,10 @@
         <v>2.14</v>
       </c>
       <c r="J6">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="K6">
-        <v>4.6399999999999997</v>
+        <v>4.64</v>
       </c>
       <c r="L6">
         <v>0.02</v>
@@ -2551,7 +2562,7 @@
         <v>3.04</v>
       </c>
       <c r="N6">
-        <v>0.55000000000000004</v>
+        <v>0.55</v>
       </c>
       <c r="O6">
         <v>1.35</v>
@@ -2560,7 +2571,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>118</v>
       </c>
@@ -2577,7 +2588,7 @@
         <v>1.9</v>
       </c>
       <c r="F7">
-        <v>-0.14000000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="G7">
         <v>0.72</v>
@@ -2585,8 +2596,17 @@
       <c r="H7">
         <v>-0.46</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I7">
+        <v>-4.77</v>
+      </c>
+      <c r="J7">
+        <v>2.39</v>
+      </c>
+      <c r="K7">
+        <v>-3.06</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>86</v>
       </c>
@@ -2612,7 +2632,7 @@
         <v>-2.86</v>
       </c>
       <c r="I8">
-        <v>4.0999999999999996</v>
+        <v>4.1</v>
       </c>
       <c r="J8">
         <v>-0.33</v>
@@ -2627,7 +2647,7 @@
         <v>1.76</v>
       </c>
       <c r="N8">
-        <v>-1.1100000000000001</v>
+        <v>-1.11</v>
       </c>
       <c r="O8">
         <v>-1.82</v>
@@ -2636,7 +2656,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -2661,8 +2681,17 @@
       <c r="H9">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I9">
+        <v>-3.99</v>
+      </c>
+      <c r="J9">
+        <v>2.94</v>
+      </c>
+      <c r="K9">
+        <v>-2.45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>104</v>
       </c>
@@ -2703,7 +2732,7 @@
         <v>11.72</v>
       </c>
       <c r="N10">
-        <v>17.920000000000002</v>
+        <v>17.92</v>
       </c>
       <c r="O10">
         <v>18.97</v>
@@ -2712,7 +2741,7 @@
         <v>18.89</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>104</v>
       </c>
@@ -2737,8 +2766,17 @@
       <c r="H11">
         <v>13.56</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I11">
+        <v>12.26</v>
+      </c>
+      <c r="J11">
+        <v>15.92</v>
+      </c>
+      <c r="K11">
+        <v>7.98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -2770,7 +2808,7 @@
         <v>-5.41</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
         <v>113</v>
       </c>
@@ -2793,10 +2831,13 @@
         <v>-1.39</v>
       </c>
       <c r="H13">
-        <v>-4.1500000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-4.15</v>
+      </c>
+      <c r="I13">
+        <v>-7.92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
         <v>132</v>
       </c>
@@ -2843,7 +2884,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
         <v>132</v>
       </c>
@@ -2868,8 +2909,17 @@
       <c r="H15">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I15">
+        <v>-2.51</v>
+      </c>
+      <c r="J15">
+        <v>3.31</v>
+      </c>
+      <c r="K15">
+        <v>-8.42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>123</v>
       </c>
@@ -2898,7 +2948,7 @@
         <v>2.73</v>
       </c>
       <c r="J16">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K16">
         <v>0.35</v>
@@ -2907,10 +2957,10 @@
         <v>-1.83</v>
       </c>
       <c r="O16">
-        <v>-0.56999999999999995</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>123</v>
       </c>
@@ -2924,7 +2974,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>99</v>
       </c>
@@ -2968,7 +3018,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -2988,13 +3038,22 @@
         <v>0.71</v>
       </c>
       <c r="G19">
-        <v>4.5199999999999996</v>
+        <v>4.52</v>
       </c>
       <c r="H19">
         <v>1.54</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I19">
+        <v>-5.44</v>
+      </c>
+      <c r="J19">
+        <v>5.36</v>
+      </c>
+      <c r="K19">
+        <v>-17.84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>109</v>
       </c>
@@ -3020,13 +3079,13 @@
         <v>-10.06</v>
       </c>
       <c r="I20">
-        <v>-0.69</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J20">
-        <v>-0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>109</v>
       </c>
@@ -3051,8 +3110,14 @@
       <c r="H21">
         <v>7.67</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I21">
+        <v>1.13</v>
+      </c>
+      <c r="J21">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -3066,16 +3131,16 @@
         <v>2025</v>
       </c>
       <c r="E22">
-        <v>4.0999999999999996</v>
+        <v>4.1</v>
       </c>
       <c r="F22">
-        <v>2.0699999999999998</v>
+        <v>2.07</v>
       </c>
       <c r="G22">
         <v>7.92</v>
       </c>
       <c r="H22">
-        <v>-9.4700000000000006</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="I22">
         <v>2.29</v>
@@ -3102,7 +3167,7 @@
         <v>-2.44</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -3116,7 +3181,7 @@
         <v>2026</v>
       </c>
       <c r="E23">
-        <v>-8.4499999999999993</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="F23">
         <v>-6.9</v>
@@ -3127,8 +3192,17 @@
       <c r="H23">
         <v>1.25</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I23">
+        <v>-9.09</v>
+      </c>
+      <c r="J23">
+        <v>-9.449999999999999</v>
+      </c>
+      <c r="K23">
+        <v>-4.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -3154,13 +3228,13 @@
         <v>-1.83</v>
       </c>
       <c r="I24">
-        <v>4.5599999999999996</v>
+        <v>4.56</v>
       </c>
       <c r="J24">
-        <v>2.5499999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -3185,8 +3259,17 @@
       <c r="H25">
         <v>5.43</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25">
+        <v>10.92</v>
+      </c>
+      <c r="K25">
+        <v>-29.07</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -3212,13 +3295,13 @@
         <v>-3.35</v>
       </c>
       <c r="I26">
-        <v>4.7300000000000004</v>
+        <v>4.73</v>
       </c>
       <c r="J26">
         <v>-0.03</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -3232,7 +3315,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>91</v>
       </c>
@@ -3255,7 +3338,7 @@
         <v>6.15</v>
       </c>
       <c r="H28">
-        <v>-2.4700000000000002</v>
+        <v>-2.47</v>
       </c>
       <c r="I28">
         <v>2.8</v>
@@ -3273,7 +3356,7 @@
         <v>7.8</v>
       </c>
       <c r="N28">
-        <v>4.4800000000000004</v>
+        <v>4.48</v>
       </c>
       <c r="O28">
         <v>2.9</v>
@@ -3282,7 +3365,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>91</v>
       </c>
@@ -3302,13 +3385,22 @@
         <v>6.52</v>
       </c>
       <c r="G29">
-        <v>8.39</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H29">
         <v>7.6</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I29">
+        <v>1.95</v>
+      </c>
+      <c r="J29">
+        <v>7.8</v>
+      </c>
+      <c r="K29">
+        <v>-4.27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -3322,7 +3414,7 @@
         <v>2025</v>
       </c>
       <c r="E30">
-        <v>8.39</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="F30">
         <v>7.5</v>
@@ -3337,7 +3429,7 @@
         <v>7.76</v>
       </c>
       <c r="J30">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="K30">
         <v>3.76</v>
@@ -3355,10 +3447,10 @@
         <v>-14.93</v>
       </c>
       <c r="P30">
-        <v>-8.36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-8.359999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -3372,19 +3464,28 @@
         <v>2026</v>
       </c>
       <c r="E31">
-        <v>-9.3000000000000007</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="F31">
         <v>-8.42</v>
       </c>
       <c r="G31">
-        <v>-9.0399999999999991</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="H31">
-        <v>-8.9700000000000006</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="I31">
+        <v>-15.59</v>
+      </c>
+      <c r="J31">
+        <v>-7.17</v>
+      </c>
+      <c r="K31">
+        <v>-9.710000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -3401,7 +3502,7 @@
         <v>-4.26</v>
       </c>
       <c r="F32">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G32">
         <v>2.41</v>
@@ -3419,7 +3520,7 @@
         <v>5.76</v>
       </c>
       <c r="L32">
-        <v>2.0099999999999998</v>
+        <v>2.01</v>
       </c>
       <c r="M32">
         <v>8.65</v>
@@ -3434,7 +3535,7 @@
         <v>10.48</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -3459,8 +3560,17 @@
       <c r="H33">
         <v>6.96</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I33">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="J33">
+        <v>8.75</v>
+      </c>
+      <c r="K33">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -3477,13 +3587,13 @@
         <v>-3.18</v>
       </c>
       <c r="F34">
-        <v>-2.5299999999999998</v>
+        <v>-2.53</v>
       </c>
       <c r="G34">
         <v>0.61</v>
       </c>
       <c r="H34">
-        <v>-9.2799999999999994</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="I34">
         <v>-1.02</v>
@@ -3495,7 +3605,7 @@
         <v>3.02</v>
       </c>
       <c r="M34">
-        <v>16.809999999999999</v>
+        <v>16.81</v>
       </c>
       <c r="N34">
         <v>19.36</v>
@@ -3504,10 +3614,10 @@
         <v>18.57</v>
       </c>
       <c r="P34">
-        <v>17.420000000000002</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <v>17.42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -3521,19 +3631,28 @@
         <v>2026</v>
       </c>
       <c r="E35">
-        <v>16.989999999999998</v>
+        <v>16.99</v>
       </c>
       <c r="F35">
         <v>15.91</v>
       </c>
       <c r="G35">
-        <v>17.190000000000001</v>
+        <v>17.19</v>
       </c>
       <c r="H35">
         <v>15.3</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I35">
+        <v>15.99</v>
+      </c>
+      <c r="J35">
+        <v>18.37</v>
+      </c>
+      <c r="K35">
+        <v>13.18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>54</v>
       </c>
@@ -3580,7 +3699,7 @@
         <v>-13.37</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>54</v>
       </c>
@@ -3605,8 +3724,17 @@
       <c r="H37">
         <v>-13.02</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I37">
+        <v>-18.17</v>
+      </c>
+      <c r="J37">
+        <v>-11.46</v>
+      </c>
+      <c r="K37">
+        <v>-16.49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>58</v>
       </c>
@@ -3647,13 +3775,13 @@
         <v>-5.54</v>
       </c>
       <c r="O38">
-        <v>-8.2200000000000006</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="P38">
         <v>-4.03</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>58</v>
       </c>
@@ -3678,8 +3806,17 @@
       <c r="H39">
         <v>-5.96</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I39">
+        <v>-10.14</v>
+      </c>
+      <c r="J39">
+        <v>-3.39</v>
+      </c>
+      <c r="K39">
+        <v>-7.23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>62</v>
       </c>
@@ -3696,13 +3833,13 @@
         <v>-1.32</v>
       </c>
       <c r="F40">
-        <v>1.1299999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="G40">
-        <v>2.1800000000000002</v>
+        <v>2.18</v>
       </c>
       <c r="H40">
-        <v>-2.2200000000000002</v>
+        <v>-2.22</v>
       </c>
       <c r="I40">
         <v>3.18</v>
@@ -3729,7 +3866,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>62</v>
       </c>
@@ -3746,7 +3883,7 @@
         <v>3.76</v>
       </c>
       <c r="F41">
-        <v>-0.28000000000000003</v>
+        <v>-0.28</v>
       </c>
       <c r="G41">
         <v>3.76</v>
@@ -3754,8 +3891,17 @@
       <c r="H41">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I41">
+        <v>-1.98</v>
+      </c>
+      <c r="J41">
+        <v>3.77</v>
+      </c>
+      <c r="K41">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>127</v>
       </c>
@@ -3793,7 +3939,7 @@
         <v>-3.91</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>127</v>
       </c>
@@ -3818,8 +3964,17 @@
       <c r="H43">
         <v>2.37</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I43">
+        <v>-2.59</v>
+      </c>
+      <c r="J43">
+        <v>3.12</v>
+      </c>
+      <c r="K43">
+        <v>5.86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>66</v>
       </c>
@@ -3848,7 +4003,7 @@
         <v>2.11</v>
       </c>
       <c r="J44">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="K44">
         <v>2.63</v>
@@ -3869,7 +4024,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>66</v>
       </c>
@@ -3894,8 +4049,17 @@
       <c r="H45">
         <v>-0.84</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I45">
+        <v>-3.72</v>
+      </c>
+      <c r="J45">
+        <v>2.06</v>
+      </c>
+      <c r="K45">
+        <v>-4.54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -3945,7 +4109,7 @@
         <v>-0.89</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
         <v>70</v>
       </c>
@@ -3970,8 +4134,17 @@
       <c r="H47">
         <v>-1</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I47">
+        <v>-9.65</v>
+      </c>
+      <c r="J47">
+        <v>-11.48</v>
+      </c>
+      <c r="K47">
+        <v>-5.65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -3988,10 +4161,10 @@
         <v>-2.11</v>
       </c>
       <c r="F48">
-        <v>2.0499999999999998</v>
+        <v>2.05</v>
       </c>
       <c r="G48">
-        <v>8.2899999999999991</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H48">
         <v>-9.42</v>
@@ -4012,16 +4185,16 @@
         <v>5.71</v>
       </c>
       <c r="N48">
-        <v>4.3499999999999996</v>
+        <v>4.35</v>
       </c>
       <c r="O48">
         <v>4.87</v>
       </c>
       <c r="P48">
-        <v>8.7799999999999994</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8.779999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -4046,8 +4219,17 @@
       <c r="H49">
         <v>4.47</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I49">
+        <v>-2.41</v>
+      </c>
+      <c r="J49">
+        <v>2.49</v>
+      </c>
+      <c r="K49">
+        <v>-4.34</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -4097,7 +4279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16">
       <c r="A51" t="s">
         <v>78</v>
       </c>
@@ -4122,8 +4304,17 @@
       <c r="H51">
         <v>-2.44</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I51">
+        <v>-3.73</v>
+      </c>
+      <c r="J51">
+        <v>-1.27</v>
+      </c>
+      <c r="K51">
+        <v>-4.09</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
       <c r="A52" t="s">
         <v>95</v>
       </c>
@@ -4137,7 +4328,7 @@
         <v>2025</v>
       </c>
       <c r="E52">
-        <v>4.3600000000000003</v>
+        <v>4.36</v>
       </c>
       <c r="F52">
         <v>2.06</v>
@@ -4155,7 +4346,7 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16">
       <c r="A53" t="s">
         <v>95</v>
       </c>
@@ -4169,7 +4360,7 @@
         <v>2026</v>
       </c>
       <c r="E53">
-        <v>5.0199999999999996</v>
+        <v>5.02</v>
       </c>
       <c r="F53">
         <v>3.86</v>
@@ -4180,8 +4371,11 @@
       <c r="H53">
         <v>1.25</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I53">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -4225,13 +4419,13 @@
         <v>3.34</v>
       </c>
       <c r="O54">
-        <v>4.6500000000000004</v>
+        <v>4.65</v>
       </c>
       <c r="P54">
         <v>6.26</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -4245,7 +4439,7 @@
         <v>2026</v>
       </c>
       <c r="E55">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="F55">
         <v>2.36</v>
@@ -4255,6 +4449,15 @@
       </c>
       <c r="H55">
         <v>3.86</v>
+      </c>
+      <c r="I55">
+        <v>-3.18</v>
+      </c>
+      <c r="J55">
+        <v>0.46</v>
+      </c>
+      <c r="K55">
+        <v>-7.38</v>
       </c>
     </row>
   </sheetData>
@@ -4263,19 +4466,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>150</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>152</v>
@@ -4311,42 +4514,42 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2">
         <v>2024</v>
       </c>
-      <c r="B2">
-        <v>2025</v>
-      </c>
       <c r="C2">
+        <v>2025</v>
+      </c>
+      <c r="D2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E2">
         <v>12</v>
       </c>
-      <c r="D2">
+      <c r="F2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I2">
+        <v>27</v>
+      </c>
+      <c r="J2">
+        <v>1.013</v>
+      </c>
+      <c r="K2">
         <v>1.3</v>
       </c>
-      <c r="E2">
-        <v>1.0129999999999999</v>
-      </c>
-      <c r="F2">
-        <v>27</v>
-      </c>
-      <c r="G2">
-        <v>0.40685799220060159</v>
-      </c>
-      <c r="H2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I2" t="s">
-        <v>164</v>
-      </c>
-      <c r="J2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s">
-        <v>149</v>
-      </c>
-      <c r="L2" t="s">
-        <v>165</v>
+      <c r="L2">
+        <v>0.4068579922006016</v>
       </c>
       <c r="M2">
         <v>0.5</v>
@@ -4355,48 +4558,48 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2025</v>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>20</v>
       </c>
       <c r="B3">
+        <v>2025</v>
+      </c>
+      <c r="C3">
         <v>2026</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1.3</v>
+      <c r="D3" t="s">
+        <v>166</v>
       </c>
       <c r="E3">
-        <v>1.0133000000000001</v>
-      </c>
-      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H3" t="s">
+        <v>165</v>
+      </c>
+      <c r="I3">
         <v>25</v>
       </c>
-      <c r="G3">
-        <v>1.3767295994479809</v>
-      </c>
-      <c r="H3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" t="s">
-        <v>141</v>
-      </c>
-      <c r="L3" t="s">
-        <v>167</v>
+      <c r="J3">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="K3">
+        <v>-0.15</v>
+      </c>
+      <c r="L3">
+        <v>1.292640383940548</v>
       </c>
       <c r="M3">
-        <v>-1.4</v>
+        <v>-2.68</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>2.38</v>
       </c>
     </row>
   </sheetData>
@@ -4405,19 +4608,19 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>150</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>152</v>
@@ -4453,136 +4656,136 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2">
         <v>2024</v>
       </c>
-      <c r="B2">
-        <v>2025</v>
-      </c>
       <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>0.8</v>
+        <v>2025</v>
+      </c>
+      <c r="D2" t="s">
+        <v>163</v>
       </c>
       <c r="E2">
-        <v>1.0078</v>
-      </c>
-      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I2">
         <v>27</v>
       </c>
-      <c r="G2">
-        <v>0.51031724070877016</v>
-      </c>
-      <c r="H2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I2" t="s">
-        <v>164</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="J2">
+        <v>1.0134</v>
+      </c>
+      <c r="K2">
+        <v>1.34</v>
+      </c>
+      <c r="L2">
+        <v>0.4204257713258387</v>
+      </c>
+      <c r="M2">
+        <v>0.52</v>
+      </c>
+      <c r="N2">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
-      <c r="K2" t="s">
-        <v>141</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="B3">
+        <v>2025</v>
+      </c>
+      <c r="C3">
+        <v>2026</v>
+      </c>
+      <c r="D3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G3" t="s">
         <v>167</v>
       </c>
-      <c r="M2">
-        <v>-0.2</v>
-      </c>
-      <c r="N2">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2025</v>
-      </c>
-      <c r="B3">
+      <c r="H3" t="s">
+        <v>165</v>
+      </c>
+      <c r="I3">
+        <v>25</v>
+      </c>
+      <c r="J3">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="K3">
+        <v>-0.15</v>
+      </c>
+      <c r="L3">
+        <v>1.292640383940548</v>
+      </c>
+      <c r="M3">
+        <v>-2.68</v>
+      </c>
+      <c r="N3">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4">
+        <v>2024</v>
+      </c>
+      <c r="C4">
         <v>2026</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1.3</v>
-      </c>
-      <c r="E3">
-        <v>1.0133000000000001</v>
-      </c>
-      <c r="F3">
-        <v>25</v>
-      </c>
-      <c r="G3">
-        <v>1.3767295994479809</v>
-      </c>
-      <c r="H3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" t="s">
-        <v>141</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="D4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G4" t="s">
         <v>167</v>
       </c>
-      <c r="M3">
-        <v>-1.4</v>
-      </c>
-      <c r="N3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2024</v>
-      </c>
-      <c r="B4">
-        <v>2026</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>2.1</v>
-      </c>
-      <c r="E4">
-        <v>1.02120374</v>
-      </c>
-      <c r="F4">
+      <c r="H4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I4">
         <v>27</v>
       </c>
-      <c r="G4">
-        <v>1.480714045495557</v>
-      </c>
-      <c r="H4" t="s">
-        <v>168</v>
-      </c>
-      <c r="I4" t="s">
-        <v>169</v>
-      </c>
-      <c r="J4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" t="s">
-        <v>141</v>
-      </c>
-      <c r="L4" t="s">
-        <v>167</v>
+      <c r="J4">
+        <v>1.0119</v>
+      </c>
+      <c r="K4">
+        <v>1.19</v>
+      </c>
+      <c r="L4">
+        <v>1.37559344073835</v>
       </c>
       <c r="M4">
-        <v>-0.8</v>
+        <v>-1.51</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>3.89</v>
       </c>
     </row>
   </sheetData>
@@ -4591,257 +4794,380 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13">
       <c r="A2">
-        <v>1.011248624878649</v>
+        <v>2025</v>
       </c>
       <c r="B2">
-        <v>1.124862487864853</v>
-      </c>
-      <c r="C2">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2">
+        <v>45992</v>
+      </c>
+      <c r="D2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2">
+        <v>1.0112</v>
+      </c>
+      <c r="G2">
+        <v>1.12</v>
+      </c>
+      <c r="H2">
+        <v>0.2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
         <v>19</v>
       </c>
-      <c r="D2">
-        <v>10.54700266558147</v>
-      </c>
-      <c r="E2">
-        <v>1.4055009632248801</v>
-      </c>
-      <c r="F2">
-        <v>0.43277943908031008</v>
-      </c>
-      <c r="G2">
-        <v>0.2</v>
-      </c>
-      <c r="H2">
+      <c r="K2">
+        <v>10.5</v>
+      </c>
+      <c r="L2">
+        <v>1.41</v>
+      </c>
+      <c r="M2">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3">
+        <v>2026</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46023</v>
+      </c>
+      <c r="D3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F3">
+        <v>1.0125</v>
+      </c>
+      <c r="G3">
+        <v>1.25</v>
+      </c>
+      <c r="H3">
+        <v>0.1</v>
+      </c>
+      <c r="I3">
+        <v>2.4</v>
+      </c>
+      <c r="J3">
+        <v>19</v>
+      </c>
+      <c r="K3">
+        <v>10.5</v>
+      </c>
+      <c r="L3">
+        <v>1.85</v>
+      </c>
+      <c r="M3">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4">
         <v>2</v>
       </c>
-      <c r="I2" t="s">
+      <c r="C4" s="2">
+        <v>46054</v>
+      </c>
+      <c r="D4" t="s">
         <v>177</v>
       </c>
-      <c r="J2" s="2">
-        <v>45992</v>
-      </c>
-      <c r="K2">
-        <v>12</v>
-      </c>
-      <c r="L2">
-        <v>2025</v>
-      </c>
-      <c r="M2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1.012465625896865</v>
-      </c>
-      <c r="B3">
-        <v>1.246562589686451</v>
-      </c>
-      <c r="C3">
+      <c r="E4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4">
+        <v>1.0117</v>
+      </c>
+      <c r="G4">
+        <v>1.17</v>
+      </c>
+      <c r="H4">
+        <v>-0.3</v>
+      </c>
+      <c r="I4">
+        <v>2.6</v>
+      </c>
+      <c r="J4">
         <v>19</v>
       </c>
-      <c r="D3">
-        <v>10.54700266558147</v>
-      </c>
-      <c r="E3">
-        <v>1.845749002399097</v>
-      </c>
-      <c r="F3">
-        <v>0.56833985805921816</v>
-      </c>
-      <c r="G3">
-        <v>0.1</v>
-      </c>
-      <c r="H3">
-        <v>2.4</v>
-      </c>
-      <c r="I3" t="s">
-        <v>179</v>
-      </c>
-      <c r="J3" s="2">
-        <v>46023</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
+      <c r="K4">
+        <v>10.5</v>
+      </c>
+      <c r="L4">
+        <v>2.22</v>
+      </c>
+      <c r="M4">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5">
         <v>2026</v>
       </c>
-      <c r="M3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1.0117000884530849</v>
-      </c>
-      <c r="B4">
-        <v>1.170008845308512</v>
-      </c>
-      <c r="C4">
-        <v>19</v>
-      </c>
-      <c r="D4">
-        <v>10.54700266558147</v>
-      </c>
-      <c r="E4">
-        <v>2.2223092564591358</v>
-      </c>
-      <c r="F4">
-        <v>0.68428964379121704</v>
-      </c>
-      <c r="G4">
-        <v>-0.3</v>
-      </c>
-      <c r="H4">
-        <v>2.6</v>
-      </c>
-      <c r="I4" t="s">
-        <v>180</v>
-      </c>
-      <c r="J4" s="2">
-        <v>46054</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46082</v>
+      </c>
+      <c r="D5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F5">
+        <v>1.0119</v>
+      </c>
+      <c r="G5">
+        <v>1.19</v>
+      </c>
+      <c r="H5">
+        <v>-0.6</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>18</v>
+      </c>
+      <c r="K5">
+        <v>9.9</v>
+      </c>
+      <c r="L5">
+        <v>2.67</v>
+      </c>
+      <c r="M5">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6">
         <v>2026</v>
       </c>
-      <c r="M4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>1.011926834967251</v>
-      </c>
-      <c r="B5">
-        <v>1.1926834967251441</v>
-      </c>
-      <c r="C5">
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2">
+        <v>46113</v>
+      </c>
+      <c r="D6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F6">
+        <v>1.0018</v>
+      </c>
+      <c r="G6">
+        <v>0.18</v>
+      </c>
+      <c r="H6">
+        <v>-2.8</v>
+      </c>
+      <c r="I6">
+        <v>3.1</v>
+      </c>
+      <c r="J6">
         <v>18</v>
       </c>
-      <c r="D5">
-        <v>9.9471847300501164</v>
-      </c>
-      <c r="E5">
-        <v>2.6662873339972628</v>
-      </c>
-      <c r="F5">
-        <v>0.8453895164929085</v>
-      </c>
-      <c r="G5">
-        <v>-0.6</v>
-      </c>
-      <c r="H5">
+      <c r="K6">
+        <v>9.9</v>
+      </c>
+      <c r="L6">
+        <v>4.44</v>
+      </c>
+      <c r="M6">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7">
+        <v>2026</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F7">
+        <v>0.9982</v>
+      </c>
+      <c r="G7">
+        <v>-0.18</v>
+      </c>
+      <c r="H7">
+        <v>-3.4</v>
+      </c>
+      <c r="I7">
         <v>3</v>
       </c>
-      <c r="I5" t="s">
-        <v>181</v>
-      </c>
-      <c r="J5" s="2">
-        <v>46082</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
+      <c r="J7">
+        <v>18</v>
+      </c>
+      <c r="K7">
+        <v>9.9</v>
+      </c>
+      <c r="L7">
+        <v>4.79</v>
+      </c>
+      <c r="M7">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8">
         <v>2026</v>
       </c>
-      <c r="M5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>1.0116086699096569</v>
-      </c>
-      <c r="B6">
-        <v>1.1608669909657141</v>
-      </c>
-      <c r="C6">
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46174</v>
+      </c>
+      <c r="D8" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F8">
+        <v>1.0001</v>
+      </c>
+      <c r="G8">
+        <v>0.01</v>
+      </c>
+      <c r="H8">
+        <v>-3.4</v>
+      </c>
+      <c r="I8">
+        <v>3.4</v>
+      </c>
+      <c r="J8">
         <v>18</v>
       </c>
-      <c r="D6">
-        <v>9.9471847300501164</v>
-      </c>
-      <c r="E6">
-        <v>3.0649618767385349</v>
-      </c>
-      <c r="F6">
-        <v>0.97179572734220843</v>
-      </c>
-      <c r="G6">
-        <v>-0.9</v>
-      </c>
-      <c r="H6">
+      <c r="K8">
+        <v>9.9</v>
+      </c>
+      <c r="L8">
+        <v>5.14</v>
+      </c>
+      <c r="M8">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9">
+        <v>2026</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46204</v>
+      </c>
+      <c r="D9" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" t="s">
+        <v>185</v>
+      </c>
+      <c r="F9">
+        <v>0.9964</v>
+      </c>
+      <c r="G9">
+        <v>-0.36</v>
+      </c>
+      <c r="H9">
+        <v>-3.9</v>
+      </c>
+      <c r="I9">
         <v>3.2</v>
       </c>
-      <c r="I6" t="s">
-        <v>182</v>
-      </c>
-      <c r="J6" s="2">
-        <v>46113</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>2026</v>
-      </c>
-      <c r="M6" t="s">
-        <v>178</v>
+      <c r="J9">
+        <v>18</v>
+      </c>
+      <c r="K9">
+        <v>9.9</v>
+      </c>
+      <c r="L9">
+        <v>5.31</v>
+      </c>
+      <c r="M9">
+        <v>1.68</v>
       </c>
     </row>
   </sheetData>
